--- a/jobs13C/diet_pos_all_tracing.xlsx
+++ b/jobs13C/diet_pos_all_tracing.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\xxing\Documents\GitHub\autopeak\jobs13C\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94EF0372-F908-4FEE-942E-8E5E83F58A99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDAE5207-9389-4FE5-889D-C16E73058C75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5505" yWindow="2280" windowWidth="19305" windowHeight="12270" xr2:uid="{987367AA-9FB7-47A2-B42F-373FA538F6FF}"/>
+    <workbookView xWindow="1725" yWindow="3315" windowWidth="24255" windowHeight="12270" xr2:uid="{987367AA-9FB7-47A2-B42F-373FA538F6FF}"/>
   </bookViews>
   <sheets>
-    <sheet name="diet_neg" sheetId="1" r:id="rId1"/>
+    <sheet name="diet_pos" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,10 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="109">
-  <si>
-    <t>file location</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="104">
   <si>
     <t>inclusion</t>
   </si>
@@ -53,105 +50,36 @@
     <t>\\gen-iota-cifs\msdata\exploris480\wlu\Unknown\20240404-ser-His-Met-tracing</t>
   </si>
   <si>
-    <t>mzxml;neg;ser-</t>
-  </si>
-  <si>
-    <t>mzxml;neg;his-</t>
-  </si>
-  <si>
-    <t>mzxml;neg;met-</t>
-  </si>
-  <si>
     <t>\\gen-iota-cifs\msdata\exploris480\wlu\Unknown\20240603-Glc-tracing</t>
   </si>
   <si>
-    <t>mzxml;neg;ctrl-</t>
-  </si>
-  <si>
-    <t>mzxml;neg;glc-</t>
-  </si>
-  <si>
     <t>\\gen-iota-cifs\msdata\exploris480\wlu\Unknown\20240618-Arg-Cys-tracing</t>
   </si>
   <si>
-    <t>mzxml;neg;cys-</t>
-  </si>
-  <si>
-    <t>mzxml;neg;arg-</t>
-  </si>
-  <si>
     <t>\\gen-iota-cifs\msdata\exploris480\wlu\Unknown\20240712-Trp-Acet-tracing</t>
   </si>
   <si>
-    <t>mzxml;neg;trp-</t>
-  </si>
-  <si>
-    <t>mzxml;neg;acet-;M19</t>
-  </si>
-  <si>
     <t>\\gen-iota-cifs\msdata\exploris480\Ricardo\Acetate-M28 Citrate-M29 mouse infusion 15Aug24</t>
   </si>
   <si>
-    <t>mzxml;neg;acet-;M28</t>
-  </si>
-  <si>
-    <t>mzxml;neg;cit-</t>
-  </si>
-  <si>
     <t>\\gen-iota-cifs\msdata\exploris480\wlu\Unknown\20240825-Jenna-13C-Thr-tracing</t>
   </si>
   <si>
-    <t>mzxml;neg;thr-</t>
-  </si>
-  <si>
     <t>\\gen-iota-cifs\msdata\exploris480\wlu\Unknown\20240909-Val-Isoleu-tracing</t>
   </si>
   <si>
-    <t>mzxml;neg;ile-</t>
-  </si>
-  <si>
-    <t>mzxml;neg;val-</t>
-  </si>
-  <si>
     <t>\\gen-iota-cifs\msdata\exploris480\wlu\Unknown\20240923-Lys-Leu-tracing</t>
   </si>
   <si>
-    <t>mzxml;neg;lys-</t>
-  </si>
-  <si>
-    <t>mzxml;neg;leu-</t>
-  </si>
-  <si>
     <t>\\gen-iota-cifs\msdata\exploris480\wlu\Unknown\20241016-Pro-Lin-tracing</t>
   </si>
   <si>
-    <t>mzxml;neg;pro-</t>
-  </si>
-  <si>
-    <t>mzxml;neg;lin-</t>
-  </si>
-  <si>
     <t>\\gen-iota-cifs\msdata\exploris480\wlu\Unknown\20241104-Inosine-Uridine-tracing</t>
   </si>
   <si>
-    <t>mzxml;neg;ino-</t>
-  </si>
-  <si>
-    <t>mzxml;neg;uri-</t>
-  </si>
-  <si>
-    <t>\\gen-iota-cifs\msdata\exploris480\wlu\Unknown\20241227-13C-gly-tracing\480K</t>
-  </si>
-  <si>
-    <t>mzxml;T</t>
-  </si>
-  <si>
     <t>M41;M43;AIF;-mz-</t>
   </si>
   <si>
-    <t>M39;M40;AIF;-mz-</t>
-  </si>
-  <si>
     <t>\\gen-iota-cifs\msdata\exploris480\Michael M\20250405 Aging Pantothenate Tissues</t>
   </si>
   <si>
@@ -164,9 +92,6 @@
     <t>\\gen-iota-cifs\msdata\exploris480\wlu\Unknown\20250505-13C-Taurine-ED</t>
   </si>
   <si>
-    <t>mzxml;neg;Tau</t>
-  </si>
-  <si>
     <t>M4;M8</t>
   </si>
   <si>
@@ -176,60 +101,18 @@
     <t>\\gen-iota-cifs\msdata\exploris480\wlu\Unknown\20250518-Vitamin-tracing</t>
   </si>
   <si>
-    <t>mzxml;neg;biotin</t>
-  </si>
-  <si>
-    <t>mzxml;neg;thia</t>
-  </si>
-  <si>
-    <t>mzxml;neg;rib</t>
-  </si>
-  <si>
-    <t>mzxml;neg;Pantothenate</t>
-  </si>
-  <si>
-    <t>mzxml;neg;control</t>
-  </si>
-  <si>
     <t>\\gen-iota-cifs\msdata\exploris480\wlu\Unknown\20250725-Fructose-palmt-oleat-tracing</t>
   </si>
   <si>
-    <t>mzxml;neg;palm</t>
-  </si>
-  <si>
-    <t>mzxml;neg;oleat</t>
-  </si>
-  <si>
-    <t>mzxml;neg;fruc;30min</t>
-  </si>
-  <si>
-    <t>mzxml;neg;fruc;60min</t>
-  </si>
-  <si>
-    <t>\\gen-iota-cifs\msdata\exploris480\Michael_M\20250721_mevalonolactone</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> \\gen-iota-cifs\msdata\exploris240\MacArthur\20250726 Mevalonate Inf Tissue</t>
-  </si>
-  <si>
     <t>\\gen-iota-cifs\msdata\exploris480\wlu\Unknown\20251111-Phe-Gln-Palm-tracing</t>
   </si>
   <si>
-    <t>mzxml;neg;phe</t>
-  </si>
-  <si>
-    <t>mzxml;neg;gln</t>
-  </si>
-  <si>
     <t>M62;M63</t>
   </si>
   <si>
     <t>\\gen-iota-cifs\msdata\exploris480\wlu\Unknown\20260118-Acetate-Mevalonate-tracing</t>
   </si>
   <si>
-    <t>mzxml;neg</t>
-  </si>
-  <si>
     <t>M71;M72;M73;blank</t>
   </si>
   <si>
@@ -239,133 +122,235 @@
     <t>output_fname</t>
   </si>
   <si>
-    <t>T01_Ser</t>
-  </si>
-  <si>
-    <t>T02_His</t>
-  </si>
-  <si>
-    <t>T03_Met</t>
-  </si>
-  <si>
-    <t>T04_Ctrl-Glc</t>
-  </si>
-  <si>
-    <t>T05_glc</t>
-  </si>
-  <si>
-    <t>T06_Cys</t>
-  </si>
-  <si>
-    <t>T07_Arg</t>
-  </si>
-  <si>
-    <t>T08_Trp</t>
-  </si>
-  <si>
-    <t>T09_Ace1</t>
-  </si>
-  <si>
-    <t>T10_Ace2</t>
-  </si>
-  <si>
-    <t>T11_Cit</t>
-  </si>
-  <si>
-    <t>T12_Thr</t>
-  </si>
-  <si>
-    <t>T13_Ile</t>
-  </si>
-  <si>
-    <t>T14_Val</t>
-  </si>
-  <si>
-    <t>T15_Lys</t>
-  </si>
-  <si>
-    <t>T16_Leu</t>
-  </si>
-  <si>
-    <t>T17_Pro</t>
-  </si>
-  <si>
-    <t>T18_Lin</t>
-  </si>
-  <si>
-    <t>T19_Ino</t>
-  </si>
-  <si>
-    <t>T20_Uri</t>
-  </si>
-  <si>
-    <t>T21_Gly</t>
-  </si>
-  <si>
-    <t>T22_Ctrl-Gly</t>
-  </si>
-  <si>
-    <t>T23_Vpan1</t>
-  </si>
-  <si>
-    <t>T24_Tau</t>
-  </si>
-  <si>
-    <t>T25_Ctrl-Tau</t>
-  </si>
-  <si>
-    <t>T26_Vbio</t>
-  </si>
-  <si>
-    <t>T27_Vthia</t>
-  </si>
-  <si>
-    <t>T28_Vrib</t>
-  </si>
-  <si>
-    <t>T29_Vpan2</t>
-  </si>
-  <si>
-    <t>T30_Ctrl-V</t>
-  </si>
-  <si>
-    <t>T31_palmt</t>
-  </si>
-  <si>
-    <t>T32_oleat</t>
-  </si>
-  <si>
-    <t>T33_Fruc_30min</t>
-  </si>
-  <si>
-    <t>T34_Fruc_60min</t>
-  </si>
-  <si>
-    <t>T35_meval_serum</t>
-  </si>
-  <si>
-    <t>T36_meval_tissue</t>
-  </si>
-  <si>
-    <t>T37_phe</t>
-  </si>
-  <si>
-    <t>T38_palmt</t>
-  </si>
-  <si>
-    <t>T39_gln</t>
-  </si>
-  <si>
-    <t>T40_meval_C2</t>
-  </si>
-  <si>
-    <t>T41_Ace3</t>
-  </si>
-  <si>
     <t>pklist</t>
   </si>
   <si>
-    <t>pklist_diet_neg_8277</t>
+    <t>pklist_diet_pos_8080</t>
+  </si>
+  <si>
+    <t>\\gen-iota-cifs\msdata\exploris480\Michael_M\20250721_mevalonolactone\scan2</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> \\gen-iota-cifs\msdata\exploris240\MacArthur\20250726 Mevalonate Inf Tissue\scan2</t>
+  </si>
+  <si>
+    <t>folder</t>
+  </si>
+  <si>
+    <t>pos_T01_Ser</t>
+  </si>
+  <si>
+    <t>pos_T02_His</t>
+  </si>
+  <si>
+    <t>pos_T03_Met</t>
+  </si>
+  <si>
+    <t>pos_T04_Ctrl-Glc</t>
+  </si>
+  <si>
+    <t>pos_T05_glc</t>
+  </si>
+  <si>
+    <t>pos_T06_Cys</t>
+  </si>
+  <si>
+    <t>pos_T07_Arg</t>
+  </si>
+  <si>
+    <t>pos_T08_Trp</t>
+  </si>
+  <si>
+    <t>pos_T09_Ace1</t>
+  </si>
+  <si>
+    <t>pos_T10_Ace2</t>
+  </si>
+  <si>
+    <t>pos_T11_Cit</t>
+  </si>
+  <si>
+    <t>pos_T12_Thr</t>
+  </si>
+  <si>
+    <t>pos_T13_Ile</t>
+  </si>
+  <si>
+    <t>pos_T14_Val</t>
+  </si>
+  <si>
+    <t>pos_T15_Lys</t>
+  </si>
+  <si>
+    <t>pos_T16_Leu</t>
+  </si>
+  <si>
+    <t>pos_T17_Pro</t>
+  </si>
+  <si>
+    <t>pos_T18_Lin</t>
+  </si>
+  <si>
+    <t>pos_T19_Ino</t>
+  </si>
+  <si>
+    <t>pos_T20_Uri</t>
+  </si>
+  <si>
+    <t>pos_T23_Vpan1</t>
+  </si>
+  <si>
+    <t>pos_T24_Tau</t>
+  </si>
+  <si>
+    <t>pos_T25_Ctrl-Tau</t>
+  </si>
+  <si>
+    <t>pos_T26_Vbio</t>
+  </si>
+  <si>
+    <t>pos_T27_Vthia</t>
+  </si>
+  <si>
+    <t>pos_T28_Vrib</t>
+  </si>
+  <si>
+    <t>pos_T29_Vpan2</t>
+  </si>
+  <si>
+    <t>pos_T30_Ctrl-V</t>
+  </si>
+  <si>
+    <t>pos_T31_palmt</t>
+  </si>
+  <si>
+    <t>pos_T32_oleat</t>
+  </si>
+  <si>
+    <t>pos_T33_Fruc_30min</t>
+  </si>
+  <si>
+    <t>pos_T34_Fruc_60min</t>
+  </si>
+  <si>
+    <t>pos_T35_meval_serum</t>
+  </si>
+  <si>
+    <t>pos_T36_meval_tissue</t>
+  </si>
+  <si>
+    <t>pos_T37_phe</t>
+  </si>
+  <si>
+    <t>pos_T38_palmt</t>
+  </si>
+  <si>
+    <t>pos_T39_gln</t>
+  </si>
+  <si>
+    <t>pos_T40_meval_C2</t>
+  </si>
+  <si>
+    <t>pos_T41_Ace3</t>
+  </si>
+  <si>
+    <t>mzxml;pos;ser-</t>
+  </si>
+  <si>
+    <t>mzxml;pos;his-</t>
+  </si>
+  <si>
+    <t>mzxml;pos;met-</t>
+  </si>
+  <si>
+    <t>mzxml;pos;ctrl-</t>
+  </si>
+  <si>
+    <t>mzxml;pos;glc-</t>
+  </si>
+  <si>
+    <t>mzxml;pos;cys-</t>
+  </si>
+  <si>
+    <t>mzxml;pos;arg-</t>
+  </si>
+  <si>
+    <t>mzxml;pos;trp-</t>
+  </si>
+  <si>
+    <t>mzxml;pos;acet-;M19</t>
+  </si>
+  <si>
+    <t>mzxml;pos;acet-;M28</t>
+  </si>
+  <si>
+    <t>mzxml;pos;cit-</t>
+  </si>
+  <si>
+    <t>mzxml;pos;thr-</t>
+  </si>
+  <si>
+    <t>mzxml;pos;ile-</t>
+  </si>
+  <si>
+    <t>mzxml;pos;val-</t>
+  </si>
+  <si>
+    <t>mzxml;pos;lys-</t>
+  </si>
+  <si>
+    <t>mzxml;pos;leu-</t>
+  </si>
+  <si>
+    <t>mzxml;pos;pro-</t>
+  </si>
+  <si>
+    <t>mzxml;pos;lin-</t>
+  </si>
+  <si>
+    <t>mzxml;pos;ino-</t>
+  </si>
+  <si>
+    <t>mzxml;pos;uri-</t>
+  </si>
+  <si>
+    <t>mzxml;pos;Tau</t>
+  </si>
+  <si>
+    <t>mzxml;pos;biotin</t>
+  </si>
+  <si>
+    <t>mzxml;pos;thia</t>
+  </si>
+  <si>
+    <t>mzxml;pos;rib</t>
+  </si>
+  <si>
+    <t>mzxml;pos;Pantothenate</t>
+  </si>
+  <si>
+    <t>mzxml;pos;control</t>
+  </si>
+  <si>
+    <t>mzxml;pos;palm</t>
+  </si>
+  <si>
+    <t>mzxml;pos;oleat</t>
+  </si>
+  <si>
+    <t>mzxml;pos;fruc;30min</t>
+  </si>
+  <si>
+    <t>mzxml;pos;fruc;60min</t>
+  </si>
+  <si>
+    <t>mzxml;pos;phe</t>
+  </si>
+  <si>
+    <t>mzxml;pos;gln</t>
+  </si>
+  <si>
+    <t>mzxml;pos</t>
   </si>
 </sst>
 </file>
@@ -435,7 +420,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -771,642 +756,610 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10984C3E-EACA-4DD3-AD3A-E289D3D20B1E}">
-  <dimension ref="A1:F42"/>
+  <dimension ref="A1:G40"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="32.42578125" customWidth="1"/>
+    <col min="1" max="1" width="85.5703125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="29.42578125" customWidth="1"/>
-    <col min="4" max="4" width="20.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="19.140625" customWidth="1"/>
-    <col min="6" max="6" width="12.5703125" customWidth="1"/>
+    <col min="4" max="4" width="22.5703125" customWidth="1"/>
+    <col min="5" max="5" width="19.28515625" customWidth="1"/>
+    <col min="8" max="8" width="17.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>65</v>
-      </c>
-      <c r="C1" t="s">
-        <v>107</v>
-      </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>1</v>
-      </c>
-      <c r="E1" t="s">
-        <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>66</v>
+        <v>32</v>
       </c>
       <c r="C2" t="s">
-        <v>108</v>
+        <v>28</v>
       </c>
       <c r="D2" t="s">
-        <v>4</v>
+        <v>71</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>67</v>
+        <v>33</v>
       </c>
       <c r="C3" t="s">
-        <v>108</v>
+        <v>28</v>
       </c>
       <c r="D3" t="s">
-        <v>5</v>
+        <v>72</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>68</v>
+        <v>34</v>
       </c>
       <c r="C4" t="s">
-        <v>108</v>
+        <v>28</v>
       </c>
       <c r="D4" t="s">
-        <v>6</v>
+        <v>73</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>69</v>
+        <v>35</v>
       </c>
       <c r="C5" t="s">
-        <v>108</v>
+        <v>28</v>
       </c>
       <c r="D5" t="s">
-        <v>8</v>
+        <v>74</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>70</v>
+        <v>36</v>
       </c>
       <c r="C6" t="s">
-        <v>108</v>
+        <v>28</v>
       </c>
       <c r="D6" t="s">
-        <v>9</v>
+        <v>75</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>71</v>
+        <v>37</v>
       </c>
       <c r="C7" t="s">
-        <v>108</v>
+        <v>28</v>
       </c>
       <c r="D7" t="s">
-        <v>11</v>
+        <v>76</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="B8" t="s">
-        <v>72</v>
+        <v>38</v>
       </c>
       <c r="C8" t="s">
-        <v>108</v>
+        <v>28</v>
       </c>
       <c r="D8" t="s">
-        <v>12</v>
+        <v>77</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="B9" t="s">
-        <v>73</v>
+        <v>39</v>
       </c>
       <c r="C9" t="s">
-        <v>108</v>
+        <v>28</v>
       </c>
       <c r="D9" t="s">
-        <v>14</v>
+        <v>78</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="B10" t="s">
-        <v>74</v>
+        <v>40</v>
       </c>
       <c r="C10" t="s">
-        <v>108</v>
+        <v>28</v>
       </c>
       <c r="D10" t="s">
-        <v>15</v>
+        <v>79</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="B11" t="s">
-        <v>75</v>
+        <v>41</v>
       </c>
       <c r="C11" t="s">
-        <v>108</v>
+        <v>28</v>
       </c>
       <c r="D11" t="s">
-        <v>17</v>
+        <v>80</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="B12" t="s">
-        <v>76</v>
+        <v>42</v>
       </c>
       <c r="C12" t="s">
-        <v>108</v>
+        <v>28</v>
       </c>
       <c r="D12" t="s">
-        <v>18</v>
+        <v>81</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="B13" t="s">
-        <v>77</v>
+        <v>43</v>
       </c>
       <c r="C13" t="s">
-        <v>108</v>
+        <v>28</v>
       </c>
       <c r="D13" t="s">
-        <v>20</v>
+        <v>82</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="B14" t="s">
-        <v>78</v>
+        <v>44</v>
       </c>
       <c r="C14" t="s">
-        <v>108</v>
+        <v>28</v>
       </c>
       <c r="D14" t="s">
-        <v>22</v>
+        <v>83</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="B15" t="s">
-        <v>79</v>
+        <v>45</v>
       </c>
       <c r="C15" t="s">
-        <v>108</v>
+        <v>28</v>
       </c>
       <c r="D15" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="B16" t="s">
-        <v>80</v>
+        <v>46</v>
       </c>
       <c r="C16" t="s">
-        <v>108</v>
+        <v>28</v>
       </c>
       <c r="D16" t="s">
-        <v>25</v>
+        <v>85</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="B17" t="s">
-        <v>81</v>
+        <v>47</v>
       </c>
       <c r="C17" t="s">
-        <v>108</v>
+        <v>28</v>
       </c>
       <c r="D17" t="s">
-        <v>26</v>
+        <v>86</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="B18" t="s">
-        <v>82</v>
+        <v>48</v>
       </c>
       <c r="C18" t="s">
-        <v>108</v>
+        <v>28</v>
       </c>
       <c r="D18" t="s">
-        <v>28</v>
+        <v>87</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="B19" t="s">
-        <v>83</v>
+        <v>49</v>
       </c>
       <c r="C19" t="s">
-        <v>108</v>
+        <v>28</v>
       </c>
       <c r="D19" t="s">
-        <v>29</v>
+        <v>88</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="B20" t="s">
-        <v>84</v>
+        <v>50</v>
       </c>
       <c r="C20" t="s">
-        <v>108</v>
+        <v>28</v>
       </c>
       <c r="D20" t="s">
-        <v>31</v>
+        <v>89</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="B21" t="s">
-        <v>85</v>
+        <v>51</v>
       </c>
       <c r="C21" t="s">
-        <v>108</v>
+        <v>28</v>
       </c>
       <c r="D21" t="s">
-        <v>32</v>
+        <v>90</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="B22" t="s">
-        <v>86</v>
+        <v>52</v>
       </c>
       <c r="C22" t="s">
-        <v>108</v>
+        <v>28</v>
       </c>
       <c r="D22" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="E22" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>33</v>
+      <c r="A23" s="2" t="s">
+        <v>16</v>
       </c>
       <c r="B23" t="s">
-        <v>87</v>
+        <v>53</v>
       </c>
       <c r="C23" t="s">
-        <v>108</v>
+        <v>28</v>
       </c>
       <c r="D23" t="s">
-        <v>34</v>
+        <v>91</v>
       </c>
       <c r="E23" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>37</v>
+      <c r="A24" s="2" t="s">
+        <v>16</v>
       </c>
       <c r="B24" t="s">
-        <v>88</v>
+        <v>54</v>
       </c>
       <c r="C24" t="s">
-        <v>108</v>
+        <v>28</v>
       </c>
       <c r="D24" t="s">
-        <v>38</v>
+        <v>91</v>
       </c>
       <c r="E24" t="s">
-        <v>39</v>
+        <v>18</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" s="2" t="s">
-        <v>40</v>
+      <c r="A25" t="s">
+        <v>19</v>
       </c>
       <c r="B25" t="s">
-        <v>89</v>
+        <v>55</v>
       </c>
       <c r="C25" t="s">
-        <v>108</v>
+        <v>28</v>
       </c>
       <c r="D25" t="s">
-        <v>41</v>
-      </c>
-      <c r="E25" t="s">
-        <v>42</v>
+        <v>92</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" s="2" t="s">
-        <v>40</v>
+      <c r="A26" t="s">
+        <v>19</v>
       </c>
       <c r="B26" t="s">
-        <v>90</v>
+        <v>56</v>
       </c>
       <c r="C26" t="s">
-        <v>108</v>
+        <v>28</v>
       </c>
       <c r="D26" t="s">
-        <v>41</v>
-      </c>
-      <c r="E26" t="s">
-        <v>43</v>
+        <v>93</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>44</v>
+        <v>19</v>
       </c>
       <c r="B27" t="s">
-        <v>91</v>
+        <v>57</v>
       </c>
       <c r="C27" t="s">
-        <v>108</v>
+        <v>28</v>
       </c>
       <c r="D27" t="s">
-        <v>45</v>
+        <v>94</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>44</v>
+        <v>19</v>
       </c>
       <c r="B28" t="s">
-        <v>92</v>
+        <v>58</v>
       </c>
       <c r="C28" t="s">
-        <v>108</v>
+        <v>28</v>
       </c>
       <c r="D28" t="s">
-        <v>46</v>
+        <v>95</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>44</v>
+        <v>19</v>
       </c>
       <c r="B29" t="s">
-        <v>93</v>
+        <v>59</v>
       </c>
       <c r="C29" t="s">
-        <v>108</v>
+        <v>28</v>
       </c>
       <c r="D29" t="s">
-        <v>47</v>
+        <v>96</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="B30" t="s">
-        <v>94</v>
+        <v>60</v>
       </c>
       <c r="C30" t="s">
-        <v>108</v>
+        <v>28</v>
       </c>
       <c r="D30" t="s">
-        <v>48</v>
+        <v>97</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="B31" t="s">
-        <v>95</v>
+        <v>61</v>
       </c>
       <c r="C31" t="s">
-        <v>108</v>
+        <v>28</v>
       </c>
       <c r="D31" t="s">
-        <v>49</v>
+        <v>98</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="B32" t="s">
-        <v>96</v>
+        <v>62</v>
       </c>
       <c r="C32" t="s">
-        <v>108</v>
+        <v>28</v>
       </c>
       <c r="D32" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="B33" t="s">
+        <v>63</v>
+      </c>
+      <c r="C33" t="s">
+        <v>28</v>
+      </c>
+      <c r="D33" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A34" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B34" t="s">
+        <v>64</v>
+      </c>
+      <c r="C34" t="s">
+        <v>28</v>
+      </c>
+      <c r="D34" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>30</v>
+      </c>
+      <c r="B35" t="s">
+        <v>65</v>
+      </c>
+      <c r="C35" t="s">
+        <v>28</v>
+      </c>
+      <c r="D35" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>21</v>
+      </c>
+      <c r="B36" t="s">
+        <v>66</v>
+      </c>
+      <c r="C36" t="s">
+        <v>28</v>
+      </c>
+      <c r="D36" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>21</v>
+      </c>
+      <c r="B37" t="s">
+        <v>67</v>
+      </c>
+      <c r="C37" t="s">
+        <v>28</v>
+      </c>
+      <c r="D37" t="s">
         <v>97</v>
       </c>
-      <c r="C33" t="s">
-        <v>108</v>
-      </c>
-      <c r="D33" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>50</v>
-      </c>
-      <c r="B34" t="s">
-        <v>98</v>
-      </c>
-      <c r="C34" t="s">
-        <v>108</v>
-      </c>
-      <c r="D34" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>50</v>
-      </c>
-      <c r="B35" t="s">
-        <v>99</v>
-      </c>
-      <c r="C35" t="s">
-        <v>108</v>
-      </c>
-      <c r="D35" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>55</v>
-      </c>
-      <c r="B36" t="s">
-        <v>100</v>
-      </c>
-      <c r="C36" t="s">
-        <v>108</v>
-      </c>
-      <c r="D36" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>56</v>
-      </c>
-      <c r="B37" t="s">
-        <v>101</v>
-      </c>
-      <c r="C37" t="s">
-        <v>108</v>
-      </c>
-      <c r="D37" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>57</v>
+      <c r="E37" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A38" s="3" t="s">
+        <v>21</v>
       </c>
       <c r="B38" t="s">
+        <v>68</v>
+      </c>
+      <c r="C38" t="s">
+        <v>28</v>
+      </c>
+      <c r="D38" t="s">
         <v>102</v>
       </c>
-      <c r="C38" t="s">
-        <v>108</v>
-      </c>
-      <c r="D38" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E38" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>57</v>
+        <v>23</v>
       </c>
       <c r="B39" t="s">
+        <v>69</v>
+      </c>
+      <c r="C39" t="s">
+        <v>28</v>
+      </c>
+      <c r="D39" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="C39" t="s">
-        <v>108</v>
-      </c>
-      <c r="D39" t="s">
-        <v>51</v>
-      </c>
       <c r="E39" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A40" s="3" t="s">
-        <v>57</v>
+        <v>24</v>
+      </c>
+      <c r="G39" s="1"/>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>23</v>
       </c>
       <c r="B40" t="s">
-        <v>104</v>
+        <v>70</v>
       </c>
       <c r="C40" t="s">
-        <v>108</v>
-      </c>
-      <c r="D40" t="s">
-        <v>59</v>
-      </c>
-      <c r="E40" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>61</v>
-      </c>
-      <c r="B41" t="s">
-        <v>105</v>
-      </c>
-      <c r="C41" t="s">
-        <v>108</v>
-      </c>
-      <c r="D41" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="E41" t="s">
-        <v>63</v>
-      </c>
-      <c r="F41" s="1"/>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>61</v>
-      </c>
-      <c r="B42" t="s">
-        <v>106</v>
-      </c>
-      <c r="C42" t="s">
-        <v>108</v>
-      </c>
-      <c r="D42" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="E42" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="F42" s="1"/>
+        <v>28</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G40" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="A25" r:id="rId1" xr:uid="{18CBE434-6DC7-4DE2-B86F-E1104EAB95B2}"/>
-    <hyperlink ref="A26" r:id="rId2" xr:uid="{EC729B26-1820-4296-B836-02393A5AF592}"/>
+    <hyperlink ref="A23" r:id="rId1" xr:uid="{7A635817-6F09-4E5C-BAD8-6BC4D0319146}"/>
+    <hyperlink ref="A24" r:id="rId2" xr:uid="{1A2FA4CC-BE48-4D9E-8E1A-FB7E2F024AAE}"/>
+    <hyperlink ref="A38" r:id="rId3" xr:uid="{70832AA8-0BAC-487F-80EE-EA2D29C6F112}"/>
+    <hyperlink ref="A34" r:id="rId4" xr:uid="{5FF62AA8-015F-43CF-A353-42D866182D02}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/jobs13C/diet_pos_all_tracing.xlsx
+++ b/jobs13C/diet_pos_all_tracing.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDAE5207-9389-4FE5-889D-C16E73058C75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1725" yWindow="3315" windowWidth="24255" windowHeight="12270" xr2:uid="{987367AA-9FB7-47A2-B42F-373FA538F6FF}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{987367AA-9FB7-47A2-B42F-373FA538F6FF}"/>
   </bookViews>
   <sheets>
     <sheet name="diet_pos" sheetId="1" r:id="rId1"/>
